--- a/jogos_2025-04-10.xlsx
+++ b/jogos_2025-04-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="224">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -265,12 +211,12 @@
     <t>Malaysia Super League</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Iran Persian Gulf Pro League</t>
   </si>
   <si>
@@ -301,12 +247,12 @@
     <t>Paraguay Division Profesional</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>South America Copa Libertadores</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -334,12 +280,12 @@
     <t>Johor Darul Ta'zim</t>
   </si>
   <si>
+    <t>Primorje</t>
+  </si>
+  <si>
     <t>ENPPI</t>
   </si>
   <si>
-    <t>Primorje</t>
-  </si>
-  <si>
     <t>Gençlerbirliği</t>
   </si>
   <si>
@@ -373,27 +319,27 @@
     <t>Ismaily SC</t>
   </si>
   <si>
+    <t>Adanaspor</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
     <t>Brann</t>
   </si>
   <si>
-    <t>Adanaspor</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>Al Ittihad</t>
   </si>
   <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
     <t>ES Mostaganem</t>
   </si>
   <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
@@ -406,39 +352,39 @@
     <t>2 de Mayo</t>
   </si>
   <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>CS Constantine</t>
   </si>
   <si>
     <t>Racing Club</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
+    <t>Inter Miami II</t>
   </si>
   <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
-  </si>
-  <si>
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Real Monarchs</t>
+  </si>
+  <si>
     <t>Colo-Colo</t>
   </si>
   <si>
-    <t>Real Monarchs</t>
+    <t>São Paulo</t>
   </si>
   <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
     <t>Los Angeles II</t>
   </si>
   <si>
@@ -457,12 +403,12 @@
     <t>Kelantan United</t>
   </si>
   <si>
+    <t>Bravo</t>
+  </si>
+  <si>
     <t>Coca-Cola</t>
   </si>
   <si>
-    <t>Bravo</t>
-  </si>
-  <si>
     <t>Ümraniyespor</t>
   </si>
   <si>
@@ -493,27 +439,27 @@
     <t>Katsina United</t>
   </si>
   <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Telavi</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
     <t>Strømsgodset</t>
   </si>
   <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Telavi</t>
-  </si>
-  <si>
     <t>Al Orubah</t>
   </si>
   <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
     <t>Oued Akbou</t>
   </si>
   <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
@@ -526,48 +472,45 @@
     <t>Deportivo Recoleta</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
+    <t>Atlético Nacional</t>
+  </si>
+  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
     <t>Atlético Bucaramanga</t>
   </si>
   <si>
-    <t>Atlético Nacional</t>
-  </si>
-  <si>
-    <t>Criciúma</t>
+    <t>Toronto II</t>
   </si>
   <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>Atlético Tembetary</t>
   </si>
   <si>
+    <t>San Jose Earthquakes II</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>San Jose Earthquakes II</t>
+    <t>Alianza Lima</t>
   </si>
   <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Alianza Lima</t>
-  </si>
-  <si>
     <t>Tacoma Defiance</t>
   </si>
   <si>
     <t>complete</t>
   </si>
   <si>
-    <t>suspended</t>
-  </si>
-  <si>
     <t>['30', '72']</t>
   </si>
   <si>
@@ -580,12 +523,12 @@
     <t>['9', '20', '25', '27', '37', '56', '58', '63', '84']</t>
   </si>
   <si>
+    <t>['24', '67', '76']</t>
+  </si>
+  <si>
     <t>['69', '90+2']</t>
   </si>
   <si>
-    <t>['24', '67', '76']</t>
-  </si>
-  <si>
     <t>['89', '90+2']</t>
   </si>
   <si>
@@ -601,27 +544,27 @@
     <t>['11', '34', '55', '72', '81', '87']</t>
   </si>
   <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['45', '60']</t>
+  </si>
+  <si>
+    <t>['47', '58', '66']</t>
+  </si>
+  <si>
     <t>['45+3', '70']</t>
   </si>
   <si>
-    <t>['49']</t>
-  </si>
-  <si>
-    <t>['47', '58', '66']</t>
-  </si>
-  <si>
-    <t>['45', '60']</t>
-  </si>
-  <si>
     <t>['45+7', '88']</t>
   </si>
   <si>
+    <t>['47']</t>
+  </si>
+  <si>
     <t>['51']</t>
   </si>
   <si>
-    <t>['47']</t>
-  </si>
-  <si>
     <t>['43']</t>
   </si>
   <si>
@@ -631,15 +574,18 @@
     <t>['6', '43']</t>
   </si>
   <si>
+    <t>['22', '84']</t>
+  </si>
+  <si>
+    <t>['50', '82', '88']</t>
+  </si>
+  <si>
+    <t>['-1', '-1']</t>
+  </si>
+  <si>
     <t>['90+2']</t>
   </si>
   <si>
-    <t>['50', '82', '88']</t>
-  </si>
-  <si>
-    <t>['22', '84']</t>
-  </si>
-  <si>
     <t>['21', '45+2', '71', '75', '76']</t>
   </si>
   <si>
@@ -649,12 +595,12 @@
     <t>['70', '76']</t>
   </si>
   <si>
+    <t>['32', '37']</t>
+  </si>
+  <si>
     <t>['7', '70']</t>
   </si>
   <si>
-    <t>['32', '37']</t>
-  </si>
-  <si>
     <t>['48', '52', '88']</t>
   </si>
   <si>
@@ -691,21 +637,21 @@
     <t>['31', '86']</t>
   </si>
   <si>
+    <t>['5', '35', '44', '90+2']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
     <t>['50']</t>
   </si>
   <si>
-    <t>['5', '35', '44', '90+2']</t>
-  </si>
-  <si>
-    <t>['28']</t>
+    <t>['8', '12', '83']</t>
   </si>
   <si>
     <t>['34']</t>
   </si>
   <si>
-    <t>['8', '12', '83']</t>
-  </si>
-  <si>
     <t>['4', '6']</t>
   </si>
   <si>
@@ -715,25 +661,28 @@
     <t>['10', '26', '39', '87']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
+  </si>
+  <si>
     <t>['54', '64']</t>
   </si>
   <si>
-    <t>['76']</t>
-  </si>
-  <si>
     <t>['80']</t>
   </si>
   <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
     <t>['-1', '-1', '-1']</t>
   </si>
   <si>
-    <t>['90+1']</t>
+    <t>['66', '76']</t>
   </si>
   <si>
     <t>['66', '81']</t>
-  </si>
-  <si>
-    <t>['66', '76']</t>
   </si>
   <si>
     <t>['15', '58']</t>
@@ -1100,10 +1049,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD42"/>
+  <dimension ref="A1:AL42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1218,79 +1167,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45757</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1305,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L2">
         <v>1.34</v>
@@ -1380,87 +1275,33 @@
         <v>1.13</v>
       </c>
       <c r="AJ2" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="AK2" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL2">
-        <v>1.02</v>
-      </c>
-      <c r="AM2">
-        <v>1.14</v>
-      </c>
-      <c r="AN2">
-        <v>2.76</v>
-      </c>
-      <c r="AO2">
-        <v>12</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.29</v>
-      </c>
-      <c r="BC2">
-        <v>4</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45757.22916666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45757</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
         <v>80</v>
       </c>
-      <c r="D3" t="s">
-        <v>98</v>
-      </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1475,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L3">
         <v>17.89</v>
@@ -1550,87 +1391,33 @@
         <v>1.52</v>
       </c>
       <c r="AJ3" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="AK3" t="s">
-        <v>214</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>16</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>0</v>
-      </c>
-      <c r="BC3">
-        <v>0</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>196</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45757.33333333334</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45757</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1645,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L4">
         <v>1.64</v>
@@ -1720,87 +1507,33 @@
         <v>1.22</v>
       </c>
       <c r="AJ4" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK4" t="s">
-        <v>215</v>
-      </c>
-      <c r="AL4">
-        <v>1.1</v>
-      </c>
-      <c r="AM4">
-        <v>1.19</v>
-      </c>
-      <c r="AN4">
-        <v>2.14</v>
-      </c>
-      <c r="AO4">
-        <v>12</v>
-      </c>
-      <c r="AP4">
-        <v>1.22</v>
-      </c>
-      <c r="AQ4">
-        <v>1.43</v>
-      </c>
-      <c r="AR4">
-        <v>1.82</v>
-      </c>
-      <c r="AS4">
-        <v>2.24</v>
-      </c>
-      <c r="AT4">
-        <v>2.97</v>
-      </c>
-      <c r="AU4">
-        <v>3.5</v>
-      </c>
-      <c r="AV4">
-        <v>2.46</v>
-      </c>
-      <c r="AW4">
-        <v>1.98</v>
-      </c>
-      <c r="AX4">
-        <v>1.52</v>
-      </c>
-      <c r="AY4">
-        <v>1.3</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.45</v>
-      </c>
-      <c r="BC4">
-        <v>2.74</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>197</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45757.33333333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45757</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1815,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L5">
         <v>2.63</v>
@@ -1890,87 +1623,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ5" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK5" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL5">
-        <v>1.49</v>
-      </c>
-      <c r="AM5">
-        <v>1.24</v>
-      </c>
-      <c r="AN5">
-        <v>1.37</v>
-      </c>
-      <c r="AO5">
-        <v>17</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>2.1</v>
-      </c>
-      <c r="BC5">
-        <v>1.73</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45757.375</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45757</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -1985,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L6">
         <v>1.02</v>
@@ -2060,427 +1739,265 @@
         <v>3.35</v>
       </c>
       <c r="AJ6" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="AK6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>10</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.06</v>
-      </c>
-      <c r="BC6">
-        <v>8</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45757.38541666666</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45757</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>1</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L7">
-        <v>3.93</v>
+        <v>3.25</v>
       </c>
       <c r="M7">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="N7">
+        <v>2.2</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
         <v>2.15</v>
       </c>
-      <c r="O7">
-        <v>2.27</v>
-      </c>
-      <c r="P7">
-        <v>5.95</v>
-      </c>
-      <c r="Q7">
-        <v>1.97</v>
-      </c>
-      <c r="R7">
-        <v>1.65</v>
-      </c>
-      <c r="S7">
-        <v>1.95</v>
-      </c>
-      <c r="T7">
-        <v>4.5</v>
-      </c>
-      <c r="U7">
-        <v>1.17</v>
-      </c>
-      <c r="V7">
-        <v>12</v>
-      </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7">
-        <v>1.18</v>
-      </c>
-      <c r="Y7">
-        <v>4.7</v>
-      </c>
-      <c r="Z7">
-        <v>1.7</v>
-      </c>
-      <c r="AA7">
-        <v>2</v>
-      </c>
-      <c r="AB7">
-        <v>3.3</v>
-      </c>
       <c r="AC7">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AD7">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="AK7" t="s">
-        <v>216</v>
-      </c>
-      <c r="AL7">
-        <v>1.49</v>
-      </c>
-      <c r="AM7">
-        <v>1.36</v>
-      </c>
-      <c r="AN7">
-        <v>1.24</v>
-      </c>
-      <c r="AO7">
-        <v>7</v>
-      </c>
-      <c r="AP7">
-        <v>1.42</v>
-      </c>
-      <c r="AQ7">
-        <v>1.7</v>
-      </c>
-      <c r="AR7">
-        <v>2.48</v>
-      </c>
-      <c r="AS7">
-        <v>2.8</v>
-      </c>
-      <c r="AT7">
-        <v>3.6</v>
-      </c>
-      <c r="AU7">
-        <v>2.77</v>
-      </c>
-      <c r="AV7">
-        <v>2.13</v>
-      </c>
-      <c r="AW7">
-        <v>1.65</v>
-      </c>
-      <c r="AX7">
-        <v>1.38</v>
-      </c>
-      <c r="AY7">
-        <v>1.25</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>2.27</v>
-      </c>
-      <c r="BC7">
-        <v>1.97</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45757.45833333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45757</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
       <c r="K8" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L8">
-        <v>3.25</v>
+        <v>3.93</v>
       </c>
       <c r="M8">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="N8">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="AC8">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ8" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="AK8" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>0</v>
-      </c>
-      <c r="BC8">
-        <v>0</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>198</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45757.45833333334</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45757</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" t="s">
         <v>80</v>
       </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -2495,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L9">
         <v>1.75</v>
@@ -2570,87 +2087,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ9" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="AK9" t="s">
-        <v>217</v>
-      </c>
-      <c r="AL9">
-        <v>1.2</v>
-      </c>
-      <c r="AM9">
-        <v>1.24</v>
-      </c>
-      <c r="AN9">
-        <v>1.87</v>
-      </c>
-      <c r="AO9">
-        <v>7</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.58</v>
-      </c>
-      <c r="BC9">
-        <v>2.52</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>199</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45757.45833333334</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45757</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2665,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L10">
         <v>2.39</v>
@@ -2740,87 +2203,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ10" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK10" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL10">
-        <v>1.39</v>
-      </c>
-      <c r="AM10">
-        <v>1.3</v>
-      </c>
-      <c r="AN10">
-        <v>1.47</v>
-      </c>
-      <c r="AO10">
-        <v>11</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.83</v>
-      </c>
-      <c r="BC10">
-        <v>2.6</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45757.47916666666</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45757</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -2835,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L11">
         <v>6.35</v>
@@ -2910,87 +2319,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ11" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="AK11" t="s">
-        <v>219</v>
-      </c>
-      <c r="AL11">
-        <v>1.22</v>
-      </c>
-      <c r="AM11">
-        <v>1.35</v>
-      </c>
-      <c r="AN11">
-        <v>1.01</v>
-      </c>
-      <c r="AO11">
-        <v>11</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>2.38</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>2.52</v>
-      </c>
-      <c r="BC11">
-        <v>1.82</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>201</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45757.5</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45757</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3005,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L12">
         <v>2</v>
@@ -3080,87 +2435,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK12" t="s">
-        <v>220</v>
-      </c>
-      <c r="AL12">
-        <v>1.22</v>
-      </c>
-      <c r="AM12">
-        <v>1.26</v>
-      </c>
-      <c r="AN12">
-        <v>1.67</v>
-      </c>
-      <c r="AO12">
-        <v>9</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.67</v>
-      </c>
-      <c r="BC12">
-        <v>2.63</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>202</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45757.5</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45757</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -3175,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L13">
         <v>1.46</v>
@@ -3250,87 +2551,33 @@
         <v>1.25</v>
       </c>
       <c r="AJ13" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="AK13" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL13">
-        <v>1.12</v>
-      </c>
-      <c r="AM13">
-        <v>1.13</v>
-      </c>
-      <c r="AN13">
-        <v>2.62</v>
-      </c>
-      <c r="AO13">
-        <v>14</v>
-      </c>
-      <c r="AP13">
-        <v>1.28</v>
-      </c>
-      <c r="AQ13">
-        <v>1.48</v>
-      </c>
-      <c r="AR13">
-        <v>1.79</v>
-      </c>
-      <c r="AS13">
-        <v>2.23</v>
-      </c>
-      <c r="AT13">
-        <v>2.85</v>
-      </c>
-      <c r="AU13">
-        <v>3.15</v>
-      </c>
-      <c r="AV13">
-        <v>2.35</v>
-      </c>
-      <c r="AW13">
-        <v>1.85</v>
-      </c>
-      <c r="AX13">
-        <v>1.54</v>
-      </c>
-      <c r="AY13">
-        <v>1.34</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.42</v>
-      </c>
-      <c r="BC13">
-        <v>2.88</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45757.53472222222</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45757</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3345,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L14">
         <v>3.03</v>
@@ -3420,87 +2667,33 @@
         <v>1.14</v>
       </c>
       <c r="AJ14" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK14" t="s">
-        <v>221</v>
-      </c>
-      <c r="AL14">
-        <v>1.3</v>
-      </c>
-      <c r="AM14">
-        <v>1.25</v>
-      </c>
-      <c r="AN14">
-        <v>1.33</v>
-      </c>
-      <c r="AO14">
-        <v>13</v>
-      </c>
-      <c r="AP14">
-        <v>1.09</v>
-      </c>
-      <c r="AQ14">
-        <v>1.17</v>
-      </c>
-      <c r="AR14">
-        <v>1.46</v>
-      </c>
-      <c r="AS14">
-        <v>1.72</v>
-      </c>
-      <c r="AT14">
-        <v>2</v>
-      </c>
-      <c r="AU14">
-        <v>5.65</v>
-      </c>
-      <c r="AV14">
-        <v>3.8</v>
-      </c>
-      <c r="AW14">
-        <v>2.57</v>
-      </c>
-      <c r="AX14">
-        <v>2</v>
-      </c>
-      <c r="AY14">
-        <v>1.73</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>2.05</v>
-      </c>
-      <c r="BC14">
-        <v>1.95</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>203</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45757.54166666666</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45757</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3515,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L15">
         <v>1.88</v>
@@ -3590,87 +2783,33 @@
         <v>1.11</v>
       </c>
       <c r="AJ15" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK15" t="s">
-        <v>222</v>
-      </c>
-      <c r="AL15">
-        <v>1.28</v>
-      </c>
-      <c r="AM15">
-        <v>1.22</v>
-      </c>
-      <c r="AN15">
-        <v>1.85</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>1.38</v>
-      </c>
-      <c r="AQ15">
-        <v>1.66</v>
-      </c>
-      <c r="AR15">
-        <v>2.06</v>
-      </c>
-      <c r="AS15">
-        <v>2.65</v>
-      </c>
-      <c r="AT15">
-        <v>3.55</v>
-      </c>
-      <c r="AU15">
-        <v>2.65</v>
-      </c>
-      <c r="AV15">
-        <v>2.02</v>
-      </c>
-      <c r="AW15">
-        <v>1.63</v>
-      </c>
-      <c r="AX15">
-        <v>1.38</v>
-      </c>
-      <c r="AY15">
-        <v>1.22</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.7</v>
-      </c>
-      <c r="BC15">
-        <v>2.45</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>204</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45757.54166666666</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45757</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -3685,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L16">
         <v>2.34</v>
@@ -3760,87 +2899,33 @@
         <v>1.12</v>
       </c>
       <c r="AJ16" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="AK16" t="s">
-        <v>223</v>
-      </c>
-      <c r="AL16">
-        <v>1.3</v>
-      </c>
-      <c r="AM16">
-        <v>1.25</v>
-      </c>
-      <c r="AN16">
-        <v>1.44</v>
-      </c>
-      <c r="AO16">
-        <v>15</v>
-      </c>
-      <c r="AP16">
-        <v>1.13</v>
-      </c>
-      <c r="AQ16">
-        <v>1.23</v>
-      </c>
-      <c r="AR16">
-        <v>1.43</v>
-      </c>
-      <c r="AS16">
-        <v>1.77</v>
-      </c>
-      <c r="AT16">
-        <v>2.21</v>
-      </c>
-      <c r="AU16">
-        <v>4.85</v>
-      </c>
-      <c r="AV16">
-        <v>3.7</v>
-      </c>
-      <c r="AW16">
-        <v>2.63</v>
-      </c>
-      <c r="AX16">
-        <v>1.9</v>
-      </c>
-      <c r="AY16">
-        <v>1.53</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.95</v>
-      </c>
-      <c r="BC16">
-        <v>2.05</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>205</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45757.54166666666</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45757</v>
       </c>
       <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
         <v>65</v>
       </c>
-      <c r="C17" t="s">
-        <v>84</v>
-      </c>
       <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
         <v>98</v>
       </c>
-      <c r="E17" t="s">
-        <v>116</v>
-      </c>
       <c r="F17" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3855,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L17">
         <v>1.89</v>
@@ -3930,87 +3015,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ17" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK17" t="s">
-        <v>224</v>
-      </c>
-      <c r="AL17">
-        <v>1.2</v>
-      </c>
-      <c r="AM17">
-        <v>1.25</v>
-      </c>
-      <c r="AN17">
-        <v>1.85</v>
-      </c>
-      <c r="AO17">
-        <v>12</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.67</v>
-      </c>
-      <c r="BC17">
-        <v>2.6</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>206</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45757.55208333334</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45757</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F18" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="G18">
         <v>6</v>
@@ -4025,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L18">
         <v>1.4</v>
@@ -4100,87 +3131,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ18" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="AK18" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL18">
-        <v>1.25</v>
-      </c>
-      <c r="AM18">
-        <v>1.2</v>
-      </c>
-      <c r="AN18">
-        <v>2.6</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
-      <c r="AQ18">
-        <v>1.95</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18">
-        <v>0</v>
-      </c>
-      <c r="AV18">
-        <v>1.85</v>
-      </c>
-      <c r="AW18">
-        <v>0</v>
-      </c>
-      <c r="AX18">
-        <v>0</v>
-      </c>
-      <c r="AY18">
-        <v>0</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.3</v>
-      </c>
-      <c r="BC18">
-        <v>5</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45757.5625</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45757</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4195,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L19">
         <v>2.96</v>
@@ -4270,427 +3247,265 @@
         <v>1</v>
       </c>
       <c r="AJ19" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK19" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL19">
-        <v>1.3</v>
-      </c>
-      <c r="AM19">
-        <v>1.4</v>
-      </c>
-      <c r="AN19">
-        <v>1.36</v>
-      </c>
-      <c r="AO19">
-        <v>4</v>
-      </c>
-      <c r="AP19">
-        <v>1.56</v>
-      </c>
-      <c r="AQ19">
-        <v>1.95</v>
-      </c>
-      <c r="AR19">
-        <v>3.05</v>
-      </c>
-      <c r="AS19">
-        <v>3.48</v>
-      </c>
-      <c r="AT19">
-        <v>4.7</v>
-      </c>
-      <c r="AU19">
-        <v>2.33</v>
-      </c>
-      <c r="AV19">
-        <v>1.79</v>
-      </c>
-      <c r="AW19">
-        <v>1.42</v>
-      </c>
-      <c r="AX19">
-        <v>1.25</v>
-      </c>
-      <c r="AY19">
-        <v>1.14</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>2.12</v>
-      </c>
-      <c r="BC19">
-        <v>2.24</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45757.58333333334</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45757</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L20">
-        <v>1.44</v>
+        <v>6.01</v>
       </c>
       <c r="M20">
-        <v>4.5</v>
+        <v>4.06</v>
       </c>
       <c r="N20">
-        <v>6.6</v>
+        <v>1.51</v>
       </c>
       <c r="O20">
-        <v>1.45</v>
+        <v>3.34</v>
       </c>
       <c r="P20">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>1.42</v>
       </c>
       <c r="R20">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
-        <v>3.65</v>
+        <v>2.89</v>
       </c>
       <c r="T20">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="U20">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="V20">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AA20">
-        <v>5.25</v>
+        <v>3.48</v>
       </c>
       <c r="AB20">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AC20">
-        <v>2.54</v>
+        <v>1.89</v>
       </c>
       <c r="AD20">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AE20">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AG20">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH20">
-        <v>3.75</v>
+        <v>6.04</v>
       </c>
       <c r="AI20">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="AK20" t="s">
-        <v>225</v>
-      </c>
-      <c r="AL20">
-        <v>1.12</v>
-      </c>
-      <c r="AM20">
-        <v>1.15</v>
-      </c>
-      <c r="AN20">
-        <v>2.55</v>
-      </c>
-      <c r="AO20">
-        <v>19</v>
-      </c>
-      <c r="AP20">
-        <v>1.24</v>
-      </c>
-      <c r="AQ20">
-        <v>1.42</v>
-      </c>
-      <c r="AR20">
-        <v>1.68</v>
-      </c>
-      <c r="AS20">
-        <v>2.05</v>
-      </c>
-      <c r="AT20">
-        <v>2.55</v>
-      </c>
-      <c r="AU20">
-        <v>3.55</v>
-      </c>
-      <c r="AV20">
-        <v>2.63</v>
-      </c>
-      <c r="AW20">
-        <v>2.05</v>
-      </c>
-      <c r="AX20">
-        <v>1.68</v>
-      </c>
-      <c r="AY20">
-        <v>1.44</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>1.45</v>
-      </c>
-      <c r="BC20">
-        <v>2.88</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>207</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45757.58333333334</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45757</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>1</v>
       </c>
-      <c r="H21">
-        <v>4</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
       <c r="J21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L21">
-        <v>6.01</v>
+        <v>1.71</v>
       </c>
       <c r="M21">
-        <v>4.06</v>
+        <v>3.3</v>
       </c>
       <c r="N21">
-        <v>1.51</v>
+        <v>4.9</v>
       </c>
       <c r="O21">
-        <v>3.34</v>
+        <v>1.56</v>
       </c>
       <c r="P21">
-        <v>9</v>
+        <v>6.95</v>
       </c>
       <c r="Q21">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="R21">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S21">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
       <c r="T21">
-        <v>2.72</v>
+        <v>3.22</v>
       </c>
       <c r="U21">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V21">
-        <v>6.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W21">
+        <v>1.04</v>
+      </c>
+      <c r="X21">
+        <v>1.07</v>
+      </c>
+      <c r="Y21">
+        <v>8</v>
+      </c>
+      <c r="Z21">
+        <v>1.39</v>
+      </c>
+      <c r="AA21">
+        <v>2.59</v>
+      </c>
+      <c r="AB21">
+        <v>2.2</v>
+      </c>
+      <c r="AC21">
+        <v>1.55</v>
+      </c>
+      <c r="AD21">
+        <v>4.1</v>
+      </c>
+      <c r="AE21">
+        <v>1.16</v>
+      </c>
+      <c r="AF21">
+        <v>2.09</v>
+      </c>
+      <c r="AG21">
+        <v>1.63</v>
+      </c>
+      <c r="AH21">
+        <v>8.5</v>
+      </c>
+      <c r="AI21">
         <v>1.06</v>
       </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>9</v>
-      </c>
-      <c r="Z21">
-        <v>1.28</v>
-      </c>
-      <c r="AA21">
-        <v>3.48</v>
-      </c>
-      <c r="AB21">
-        <v>1.89</v>
-      </c>
-      <c r="AC21">
-        <v>1.89</v>
-      </c>
-      <c r="AD21">
-        <v>3.2</v>
-      </c>
-      <c r="AE21">
-        <v>1.32</v>
-      </c>
-      <c r="AF21">
-        <v>1.92</v>
-      </c>
-      <c r="AG21">
-        <v>1.75</v>
-      </c>
-      <c r="AH21">
-        <v>6.04</v>
-      </c>
-      <c r="AI21">
-        <v>1.11</v>
-      </c>
       <c r="AJ21" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AK21" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL21">
-        <v>2.38</v>
-      </c>
-      <c r="AM21">
-        <v>1.19</v>
-      </c>
-      <c r="AN21">
-        <v>1.09</v>
-      </c>
-      <c r="AO21">
-        <v>13</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>3.34</v>
-      </c>
-      <c r="BC21">
-        <v>1.42</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45757.58333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45757</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G22">
         <v>3</v>
@@ -4705,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L22">
         <v>1.43</v>
@@ -4780,93 +3595,39 @@
         <v>1.25</v>
       </c>
       <c r="AJ22" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="AK22" t="s">
-        <v>227</v>
-      </c>
-      <c r="AL22">
-        <v>1.11</v>
-      </c>
-      <c r="AM22">
-        <v>1.17</v>
-      </c>
-      <c r="AN22">
-        <v>2.82</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>1.23</v>
-      </c>
-      <c r="AQ22">
-        <v>1.4</v>
-      </c>
-      <c r="AR22">
-        <v>1.65</v>
-      </c>
-      <c r="AS22">
-        <v>2</v>
-      </c>
-      <c r="AT22">
-        <v>2.55</v>
-      </c>
-      <c r="AU22">
-        <v>3.65</v>
-      </c>
-      <c r="AV22">
-        <v>2.65</v>
-      </c>
-      <c r="AW22">
-        <v>2.08</v>
-      </c>
-      <c r="AX22">
-        <v>1.71</v>
-      </c>
-      <c r="AY22">
-        <v>1.45</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1.3</v>
-      </c>
-      <c r="BC22">
-        <v>3.4</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45757.58333333334</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45757</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -4875,162 +3636,108 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L23">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="M23">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N23">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="O23">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="P23">
-        <v>6.95</v>
+        <v>17</v>
       </c>
       <c r="Q23">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="R23">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="S23">
-        <v>2.43</v>
+        <v>3.65</v>
       </c>
       <c r="T23">
-        <v>3.22</v>
+        <v>2.1</v>
       </c>
       <c r="U23">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="V23">
-        <v>8.699999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z23">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AA23">
-        <v>2.59</v>
+        <v>5.25</v>
       </c>
       <c r="AB23">
+        <v>1.48</v>
+      </c>
+      <c r="AC23">
+        <v>2.54</v>
+      </c>
+      <c r="AD23">
+        <v>2.05</v>
+      </c>
+      <c r="AE23">
+        <v>1.65</v>
+      </c>
+      <c r="AF23">
+        <v>1.57</v>
+      </c>
+      <c r="AG23">
         <v>2.2</v>
       </c>
-      <c r="AC23">
-        <v>1.55</v>
-      </c>
-      <c r="AD23">
-        <v>4.1</v>
-      </c>
-      <c r="AE23">
-        <v>1.16</v>
-      </c>
-      <c r="AF23">
-        <v>2.09</v>
-      </c>
-      <c r="AG23">
-        <v>1.63</v>
-      </c>
       <c r="AH23">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="AI23">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AJ23" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="AK23" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL23">
-        <v>1.12</v>
-      </c>
-      <c r="AM23">
-        <v>1.24</v>
-      </c>
-      <c r="AN23">
-        <v>1.94</v>
-      </c>
-      <c r="AO23">
-        <v>8</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>1.56</v>
-      </c>
-      <c r="BC23">
-        <v>3.02</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>209</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45757.58333333334</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45757</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -5045,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L24">
         <v>1.15</v>
@@ -5120,427 +3827,265 @@
         <v>1.35</v>
       </c>
       <c r="AJ24" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="AK24" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL24">
-        <v>1.03</v>
-      </c>
-      <c r="AM24">
-        <v>1.08</v>
-      </c>
-      <c r="AN24">
-        <v>4.75</v>
-      </c>
-      <c r="AO24">
-        <v>8</v>
-      </c>
-      <c r="AP24">
-        <v>1.34</v>
-      </c>
-      <c r="AQ24">
-        <v>1.58</v>
-      </c>
-      <c r="AR24">
-        <v>1.94</v>
-      </c>
-      <c r="AS24">
-        <v>2.48</v>
-      </c>
-      <c r="AT24">
-        <v>3.2</v>
-      </c>
-      <c r="AU24">
-        <v>2.85</v>
-      </c>
-      <c r="AV24">
-        <v>2.12</v>
-      </c>
-      <c r="AW24">
-        <v>1.71</v>
-      </c>
-      <c r="AX24">
-        <v>1.44</v>
-      </c>
-      <c r="AY24">
-        <v>1.27</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>1.22</v>
-      </c>
-      <c r="BC24">
-        <v>4.33</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45757.625</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45757</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L25">
-        <v>1.74</v>
+        <v>2.87</v>
       </c>
       <c r="M25">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N25">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="P25">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q25">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="R25">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S25">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="T25">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U25">
         <v>1.18</v>
       </c>
       <c r="V25">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y25">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA25">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB25">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AC25">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AD25">
         <v>5.5</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="AG25">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AH25">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AI25">
         <v>1.03</v>
       </c>
       <c r="AJ25" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="AK25" t="s">
-        <v>228</v>
-      </c>
-      <c r="AL25">
-        <v>1.04</v>
-      </c>
-      <c r="AM25">
-        <v>1.33</v>
-      </c>
-      <c r="AN25">
-        <v>2</v>
-      </c>
-      <c r="AO25">
-        <v>6</v>
-      </c>
-      <c r="AP25">
-        <v>1.57</v>
-      </c>
-      <c r="AQ25">
-        <v>2.07</v>
-      </c>
-      <c r="AR25">
-        <v>2.7</v>
-      </c>
-      <c r="AS25">
-        <v>3.68</v>
-      </c>
-      <c r="AT25">
-        <v>5.15</v>
-      </c>
-      <c r="AU25">
-        <v>2.18</v>
-      </c>
-      <c r="AV25">
-        <v>1.71</v>
-      </c>
-      <c r="AW25">
-        <v>1.36</v>
-      </c>
-      <c r="AX25">
-        <v>1.22</v>
-      </c>
-      <c r="AY25">
-        <v>1.11</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>1.57</v>
-      </c>
-      <c r="BC25">
-        <v>3.2</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>210</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45757.625</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45757</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L26">
-        <v>2.87</v>
+        <v>1.74</v>
       </c>
       <c r="M26">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N26">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="P26">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="R26">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S26">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="T26">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U26">
         <v>1.18</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="W26">
         <v>1.02</v>
       </c>
       <c r="X26">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y26">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z26">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA26">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB26">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AC26">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AD26">
         <v>5.5</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="AG26">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AH26">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AI26">
         <v>1.03</v>
       </c>
       <c r="AJ26" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="AK26" t="s">
-        <v>229</v>
-      </c>
-      <c r="AL26">
-        <v>1.4</v>
-      </c>
-      <c r="AM26">
-        <v>1.38</v>
-      </c>
-      <c r="AN26">
-        <v>1.31</v>
-      </c>
-      <c r="AO26">
-        <v>7</v>
-      </c>
-      <c r="AP26">
-        <v>1.57</v>
-      </c>
-      <c r="AQ26">
-        <v>1.98</v>
-      </c>
-      <c r="AR26">
-        <v>2.52</v>
-      </c>
-      <c r="AS26">
-        <v>3.4</v>
-      </c>
-      <c r="AT26">
-        <v>4.75</v>
-      </c>
-      <c r="AU26">
-        <v>2.32</v>
-      </c>
-      <c r="AV26">
-        <v>1.75</v>
-      </c>
-      <c r="AW26">
-        <v>1.41</v>
-      </c>
-      <c r="AX26">
-        <v>1.25</v>
-      </c>
-      <c r="AY26">
-        <v>1.13</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>2.63</v>
-      </c>
-      <c r="BC26">
-        <v>1.73</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>211</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45757.625</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45757</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -5555,7 +4100,7 @@
         <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L27">
         <v>2.11</v>
@@ -5630,87 +4175,33 @@
         <v>1.11</v>
       </c>
       <c r="AJ27" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="AK27" t="s">
-        <v>230</v>
-      </c>
-      <c r="AL27">
-        <v>1.31</v>
-      </c>
-      <c r="AM27">
-        <v>1.28</v>
-      </c>
-      <c r="AN27">
-        <v>1.65</v>
-      </c>
-      <c r="AO27">
-        <v>15</v>
-      </c>
-      <c r="AP27">
-        <v>1.15</v>
-      </c>
-      <c r="AQ27">
-        <v>1.29</v>
-      </c>
-      <c r="AR27">
-        <v>1.66</v>
-      </c>
-      <c r="AS27">
-        <v>1.86</v>
-      </c>
-      <c r="AT27">
-        <v>2.34</v>
-      </c>
-      <c r="AU27">
-        <v>4.5</v>
-      </c>
-      <c r="AV27">
-        <v>3.15</v>
-      </c>
-      <c r="AW27">
-        <v>2.35</v>
-      </c>
-      <c r="AX27">
-        <v>1.88</v>
-      </c>
-      <c r="AY27">
-        <v>1.49</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>1.8</v>
-      </c>
-      <c r="BC27">
-        <v>2.35</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>212</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45757.65625</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45757</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -5725,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L28">
         <v>1.79</v>
@@ -5800,87 +4291,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ28" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="AK28" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL28">
-        <v>1.18</v>
-      </c>
-      <c r="AM28">
-        <v>1.27</v>
-      </c>
-      <c r="AN28">
-        <v>2.07</v>
-      </c>
-      <c r="AO28">
-        <v>6</v>
-      </c>
-      <c r="AP28">
-        <v>1.32</v>
-      </c>
-      <c r="AQ28">
-        <v>1.54</v>
-      </c>
-      <c r="AR28">
-        <v>1.88</v>
-      </c>
-      <c r="AS28">
-        <v>2.4</v>
-      </c>
-      <c r="AT28">
-        <v>3.15</v>
-      </c>
-      <c r="AU28">
-        <v>3.05</v>
-      </c>
-      <c r="AV28">
-        <v>2.3</v>
-      </c>
-      <c r="AW28">
-        <v>1.8</v>
-      </c>
-      <c r="AX28">
-        <v>1.5</v>
-      </c>
-      <c r="AY28">
-        <v>1.3</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>1.58</v>
-      </c>
-      <c r="BC28">
-        <v>2.81</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>213</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45757.66666666666</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45757</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -5895,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L29">
         <v>1.35</v>
@@ -5970,87 +4407,33 @@
         <v>1.14</v>
       </c>
       <c r="AJ29" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="AK29" t="s">
-        <v>227</v>
-      </c>
-      <c r="AL29">
-        <v>1.03</v>
-      </c>
-      <c r="AM29">
-        <v>1.15</v>
-      </c>
-      <c r="AN29">
-        <v>2.8</v>
-      </c>
-      <c r="AO29">
-        <v>17</v>
-      </c>
-      <c r="AP29">
-        <v>0</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29">
-        <v>0</v>
-      </c>
-      <c r="AV29">
-        <v>0</v>
-      </c>
-      <c r="AW29">
-        <v>0</v>
-      </c>
-      <c r="AX29">
-        <v>0</v>
-      </c>
-      <c r="AY29">
-        <v>0</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.25</v>
-      </c>
-      <c r="BC29">
-        <v>4.75</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45757.72916666666</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45757</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E30" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6065,7 +4448,7 @@
         <v>3</v>
       </c>
       <c r="K30" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L30">
         <v>2.27</v>
@@ -6140,263 +4523,155 @@
         <v>1.01</v>
       </c>
       <c r="AJ30" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="AK30" t="s">
-        <v>232</v>
-      </c>
-      <c r="AL30">
-        <v>1.36</v>
-      </c>
-      <c r="AM30">
-        <v>1.31</v>
-      </c>
-      <c r="AN30">
-        <v>1.62</v>
-      </c>
-      <c r="AO30">
-        <v>7</v>
-      </c>
-      <c r="AP30">
-        <v>1.48</v>
-      </c>
-      <c r="AQ30">
-        <v>1.9</v>
-      </c>
-      <c r="AR30">
-        <v>2.4</v>
-      </c>
-      <c r="AS30">
-        <v>3.3</v>
-      </c>
-      <c r="AT30">
-        <v>4.2</v>
-      </c>
-      <c r="AU30">
-        <v>2.25</v>
-      </c>
-      <c r="AV30">
-        <v>1.76</v>
-      </c>
-      <c r="AW30">
-        <v>1.51</v>
-      </c>
-      <c r="AX30">
-        <v>1.28</v>
-      </c>
-      <c r="AY30">
-        <v>1.17</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>1.73</v>
-      </c>
-      <c r="BC30">
-        <v>2.44</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>214</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45757.75</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45757</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ31" t="s">
         <v>186</v>
       </c>
       <c r="AK31" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>0</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31">
-        <v>0</v>
-      </c>
-      <c r="AV31">
-        <v>0</v>
-      </c>
-      <c r="AW31">
-        <v>0</v>
-      </c>
-      <c r="AX31">
-        <v>0</v>
-      </c>
-      <c r="AY31">
-        <v>0</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>0</v>
-      </c>
-      <c r="BC31">
-        <v>0</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>215</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45757.79166666666</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45757</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E32" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -6405,37 +4680,37 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L32">
+        <v>1.49</v>
+      </c>
+      <c r="M32">
+        <v>3.98</v>
+      </c>
+      <c r="N32">
+        <v>6.7</v>
+      </c>
+      <c r="O32">
         <v>1.36</v>
       </c>
-      <c r="M32">
-        <v>4.3</v>
-      </c>
-      <c r="N32">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="O32">
-        <v>1.25</v>
-      </c>
       <c r="P32">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="R32">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S32">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T32">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -6444,129 +4719,75 @@
         <v>1.06</v>
       </c>
       <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z32">
+        <v>1.33</v>
+      </c>
+      <c r="AA32">
+        <v>2.92</v>
+      </c>
+      <c r="AB32">
+        <v>2.05</v>
+      </c>
+      <c r="AC32">
+        <v>1.65</v>
+      </c>
+      <c r="AD32">
+        <v>3.88</v>
+      </c>
+      <c r="AE32">
+        <v>1.2</v>
+      </c>
+      <c r="AF32">
+        <v>2.38</v>
+      </c>
+      <c r="AG32">
+        <v>1.53</v>
+      </c>
+      <c r="AH32">
+        <v>7.9</v>
+      </c>
+      <c r="AI32">
         <v>1.02</v>
       </c>
-      <c r="Y32">
-        <v>7.8</v>
-      </c>
-      <c r="Z32">
-        <v>1.37</v>
-      </c>
-      <c r="AA32">
-        <v>2.74</v>
-      </c>
-      <c r="AB32">
-        <v>2</v>
-      </c>
-      <c r="AC32">
-        <v>1.75</v>
-      </c>
-      <c r="AD32">
-        <v>4.2</v>
-      </c>
-      <c r="AE32">
-        <v>1.17</v>
-      </c>
-      <c r="AF32">
-        <v>2.75</v>
-      </c>
-      <c r="AG32">
-        <v>1.4</v>
-      </c>
-      <c r="AH32">
-        <v>9</v>
-      </c>
-      <c r="AI32">
-        <v>1</v>
-      </c>
       <c r="AJ32" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="AK32" t="s">
-        <v>233</v>
-      </c>
-      <c r="AL32">
-        <v>1.06</v>
-      </c>
-      <c r="AM32">
-        <v>1.21</v>
-      </c>
-      <c r="AN32">
-        <v>2.9</v>
-      </c>
-      <c r="AO32">
-        <v>-1</v>
-      </c>
-      <c r="AP32">
-        <v>1.36</v>
-      </c>
-      <c r="AQ32">
-        <v>1.61</v>
-      </c>
-      <c r="AR32">
-        <v>1.97</v>
-      </c>
-      <c r="AS32">
-        <v>2.5</v>
-      </c>
-      <c r="AT32">
-        <v>3.2</v>
-      </c>
-      <c r="AU32">
-        <v>2.8</v>
-      </c>
-      <c r="AV32">
-        <v>2.15</v>
-      </c>
-      <c r="AW32">
-        <v>1.72</v>
-      </c>
-      <c r="AX32">
-        <v>1.46</v>
-      </c>
-      <c r="AY32">
-        <v>1.28</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>1.25</v>
-      </c>
-      <c r="BC32">
-        <v>5.5</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45757.79166666666</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45757</v>
       </c>
       <c r="B33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" t="s">
         <v>73</v>
       </c>
-      <c r="C33" t="s">
-        <v>95</v>
-      </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -6575,672 +4796,456 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L33">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="M33">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="N33">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="O33">
         <v>1.36</v>
       </c>
       <c r="P33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>3.75</v>
       </c>
       <c r="R33">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC33">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AD33">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="AK33" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL33">
-        <v>1.11</v>
-      </c>
-      <c r="AM33">
-        <v>1.23</v>
-      </c>
-      <c r="AN33">
-        <v>2.5</v>
-      </c>
-      <c r="AO33">
-        <v>-1</v>
-      </c>
-      <c r="AP33">
-        <v>1.44</v>
-      </c>
-      <c r="AQ33">
-        <v>1.72</v>
-      </c>
-      <c r="AR33">
-        <v>2.12</v>
-      </c>
-      <c r="AS33">
-        <v>2.7</v>
-      </c>
-      <c r="AT33">
-        <v>3.55</v>
-      </c>
-      <c r="AU33">
-        <v>2.55</v>
-      </c>
-      <c r="AV33">
-        <v>1.98</v>
-      </c>
-      <c r="AW33">
-        <v>1.63</v>
-      </c>
-      <c r="AX33">
-        <v>1.38</v>
-      </c>
-      <c r="AY33">
-        <v>1.24</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>1.36</v>
-      </c>
-      <c r="BC33">
-        <v>3.75</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>216</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45757.79166666666</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45757</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E34" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
         <v>2</v>
       </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
       <c r="I34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L34">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="M34">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N34">
-        <v>5.15</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O34">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="P34">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q34">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="R34">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S34">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T34">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V34">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="Z34">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AA34">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="AB34">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC34">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD34">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AE34">
         <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AG34">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AH34">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AI34">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AJ34" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="AK34" t="s">
-        <v>234</v>
-      </c>
-      <c r="AL34">
-        <v>1.33</v>
-      </c>
-      <c r="AM34">
-        <v>1.2</v>
-      </c>
-      <c r="AN34">
-        <v>1.91</v>
-      </c>
-      <c r="AO34">
-        <v>9</v>
-      </c>
-      <c r="AP34">
-        <v>1.17</v>
-      </c>
-      <c r="AQ34">
-        <v>1.29</v>
-      </c>
-      <c r="AR34">
-        <v>1.66</v>
-      </c>
-      <c r="AS34">
-        <v>1.77</v>
-      </c>
-      <c r="AT34">
-        <v>2.34</v>
-      </c>
-      <c r="AU34">
-        <v>4.35</v>
-      </c>
-      <c r="AV34">
-        <v>3.15</v>
-      </c>
-      <c r="AW34">
-        <v>2.35</v>
-      </c>
-      <c r="AX34">
-        <v>1.86</v>
-      </c>
-      <c r="AY34">
-        <v>1.5</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>1.48</v>
-      </c>
-      <c r="BC34">
-        <v>3.35</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>217</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45757.79166666666</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45757</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E35" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L35">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M35">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N35">
+        <v>2.61</v>
+      </c>
+      <c r="O35">
+        <v>2.1</v>
+      </c>
+      <c r="P35">
+        <v>20.5</v>
+      </c>
+      <c r="Q35">
+        <v>1.73</v>
+      </c>
+      <c r="R35">
+        <v>1.32</v>
+      </c>
+      <c r="S35">
+        <v>2.99</v>
+      </c>
+      <c r="T35">
+        <v>2.61</v>
+      </c>
+      <c r="U35">
+        <v>1.41</v>
+      </c>
+      <c r="V35">
+        <v>4.5</v>
+      </c>
+      <c r="W35">
+        <v>1.17</v>
+      </c>
+      <c r="X35">
+        <v>1</v>
+      </c>
+      <c r="Y35">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z35">
+        <v>1.13</v>
+      </c>
+      <c r="AA35">
         <v>3.8</v>
       </c>
-      <c r="O35">
-        <v>1.67</v>
-      </c>
-      <c r="P35">
-        <v>22</v>
-      </c>
-      <c r="Q35">
+      <c r="AB35">
+        <v>1.48</v>
+      </c>
+      <c r="AC35">
+        <v>2.05</v>
+      </c>
+      <c r="AD35">
         <v>2.2</v>
       </c>
-      <c r="R35">
-        <v>1.25</v>
-      </c>
-      <c r="S35">
-        <v>3.8</v>
-      </c>
-      <c r="T35">
-        <v>2.08</v>
-      </c>
-      <c r="U35">
-        <v>1.7</v>
-      </c>
-      <c r="V35">
-        <v>3.6</v>
-      </c>
-      <c r="W35">
-        <v>1.2</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>1.1</v>
-      </c>
-      <c r="AA35">
-        <v>5.75</v>
-      </c>
-      <c r="AB35">
-        <v>1.4</v>
-      </c>
-      <c r="AC35">
-        <v>2.75</v>
-      </c>
-      <c r="AD35">
-        <v>1.85</v>
-      </c>
       <c r="AE35">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AF35">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AG35">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AH35">
-        <v>3.08</v>
+        <v>4.9</v>
       </c>
       <c r="AI35">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AJ35" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="AK35" t="s">
-        <v>220</v>
-      </c>
-      <c r="AL35">
-        <v>1.18</v>
-      </c>
-      <c r="AM35">
-        <v>1.19</v>
-      </c>
-      <c r="AN35">
-        <v>1.57</v>
-      </c>
-      <c r="AO35">
-        <v>7</v>
-      </c>
-      <c r="AP35">
-        <v>0</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>1.7</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>0</v>
-      </c>
-      <c r="AV35">
-        <v>0</v>
-      </c>
-      <c r="AW35">
-        <v>2.05</v>
-      </c>
-      <c r="AX35">
-        <v>0</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.67</v>
-      </c>
-      <c r="BC35">
-        <v>2.2</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>218</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45757.83333333334</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45757</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E36" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L36">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M36">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N36">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
       <c r="O36">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="P36">
-        <v>20.5</v>
+        <v>22</v>
       </c>
       <c r="Q36">
+        <v>2.2</v>
+      </c>
+      <c r="R36">
+        <v>1.25</v>
+      </c>
+      <c r="S36">
+        <v>3.8</v>
+      </c>
+      <c r="T36">
+        <v>2.08</v>
+      </c>
+      <c r="U36">
+        <v>1.7</v>
+      </c>
+      <c r="V36">
+        <v>3.6</v>
+      </c>
+      <c r="W36">
+        <v>1.2</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>1.1</v>
+      </c>
+      <c r="AA36">
+        <v>5.75</v>
+      </c>
+      <c r="AB36">
+        <v>1.4</v>
+      </c>
+      <c r="AC36">
+        <v>2.75</v>
+      </c>
+      <c r="AD36">
+        <v>1.85</v>
+      </c>
+      <c r="AE36">
         <v>1.73</v>
       </c>
-      <c r="R36">
+      <c r="AF36">
         <v>1.32</v>
       </c>
-      <c r="S36">
-        <v>2.99</v>
-      </c>
-      <c r="T36">
-        <v>2.61</v>
-      </c>
-      <c r="U36">
-        <v>1.41</v>
-      </c>
-      <c r="V36">
-        <v>4.5</v>
-      </c>
-      <c r="W36">
-        <v>1.17</v>
-      </c>
-      <c r="X36">
-        <v>1</v>
-      </c>
-      <c r="Y36">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z36">
-        <v>1.13</v>
-      </c>
-      <c r="AA36">
-        <v>3.8</v>
-      </c>
-      <c r="AB36">
-        <v>1.48</v>
-      </c>
-      <c r="AC36">
-        <v>2.05</v>
-      </c>
-      <c r="AD36">
-        <v>2.2</v>
-      </c>
-      <c r="AE36">
-        <v>1.31</v>
-      </c>
-      <c r="AF36">
-        <v>1.42</v>
-      </c>
       <c r="AG36">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AH36">
-        <v>4.9</v>
+        <v>3.08</v>
       </c>
       <c r="AI36">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AJ36" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AK36" t="s">
-        <v>235</v>
-      </c>
-      <c r="AL36">
-        <v>1.25</v>
-      </c>
-      <c r="AM36">
-        <v>1.2</v>
-      </c>
-      <c r="AN36">
-        <v>1.37</v>
-      </c>
-      <c r="AO36">
-        <v>5</v>
-      </c>
-      <c r="AP36">
-        <v>0</v>
-      </c>
-      <c r="AQ36">
-        <v>1.85</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>0</v>
-      </c>
-      <c r="AV36">
-        <v>1.85</v>
-      </c>
-      <c r="AW36">
-        <v>0</v>
-      </c>
-      <c r="AX36">
-        <v>0</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>2.1</v>
-      </c>
-      <c r="BC36">
-        <v>1.73</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>202</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45757.83333333334</v>
       </c>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>45757</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E37" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F37" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -7255,7 +5260,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L37">
         <v>2.15</v>
@@ -7330,93 +5335,39 @@
         <v>1.07</v>
       </c>
       <c r="AJ37" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="AK37" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL37">
-        <v>1.31</v>
-      </c>
-      <c r="AM37">
-        <v>1.31</v>
-      </c>
-      <c r="AN37">
-        <v>1.66</v>
-      </c>
-      <c r="AO37">
-        <v>9</v>
-      </c>
-      <c r="AP37">
-        <v>1.52</v>
-      </c>
-      <c r="AQ37">
-        <v>1.86</v>
-      </c>
-      <c r="AR37">
-        <v>2.78</v>
-      </c>
-      <c r="AS37">
-        <v>3.05</v>
-      </c>
-      <c r="AT37">
-        <v>4.33</v>
-      </c>
-      <c r="AU37">
-        <v>2.3</v>
-      </c>
-      <c r="AV37">
-        <v>1.77</v>
-      </c>
-      <c r="AW37">
-        <v>1.55</v>
-      </c>
-      <c r="AX37">
-        <v>1.29</v>
-      </c>
-      <c r="AY37">
-        <v>1.17</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>1.76</v>
-      </c>
-      <c r="BC37">
-        <v>2.36</v>
-      </c>
-      <c r="BD37" s="3">
+        <v>174</v>
+      </c>
+      <c r="AL37" s="3">
         <v>45757.84375</v>
       </c>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>45757</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E38" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F38" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -7425,168 +5376,114 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L38">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="M38">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="N38">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="O38">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="P38">
-        <v>7</v>
+        <v>16.25</v>
       </c>
       <c r="Q38">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S38">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="U38">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AA38">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AB38">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AC38">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AD38">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AE38">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="AF38">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AG38">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AH38">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="AI38">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ38" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="AK38" t="s">
-        <v>236</v>
-      </c>
-      <c r="AL38">
-        <v>1.36</v>
-      </c>
-      <c r="AM38">
-        <v>1.3</v>
-      </c>
-      <c r="AN38">
-        <v>1.53</v>
-      </c>
-      <c r="AO38">
-        <v>-1</v>
-      </c>
-      <c r="AP38">
-        <v>1.33</v>
-      </c>
-      <c r="AQ38">
-        <v>1.58</v>
-      </c>
-      <c r="AR38">
-        <v>1.95</v>
-      </c>
-      <c r="AS38">
-        <v>2.43</v>
-      </c>
-      <c r="AT38">
-        <v>3.15</v>
-      </c>
-      <c r="AU38">
-        <v>2.95</v>
-      </c>
-      <c r="AV38">
-        <v>2.2</v>
-      </c>
-      <c r="AW38">
-        <v>1.7</v>
-      </c>
-      <c r="AX38">
-        <v>1.48</v>
-      </c>
-      <c r="AY38">
-        <v>1.29</v>
-      </c>
-      <c r="AZ38">
-        <v>0</v>
-      </c>
-      <c r="BA38">
-        <v>0</v>
-      </c>
-      <c r="BB38">
-        <v>1.95</v>
-      </c>
-      <c r="BC38">
-        <v>2.2</v>
-      </c>
-      <c r="BD38" s="3">
+        <v>219</v>
+      </c>
+      <c r="AL38" s="3">
         <v>45757.875</v>
       </c>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>45757</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E39" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -7595,162 +5492,108 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L39">
+        <v>2.31</v>
+      </c>
+      <c r="M39">
+        <v>3.06</v>
+      </c>
+      <c r="N39">
+        <v>3.23</v>
+      </c>
+      <c r="O39">
+        <v>1.95</v>
+      </c>
+      <c r="P39">
+        <v>7</v>
+      </c>
+      <c r="Q39">
+        <v>2.2</v>
+      </c>
+      <c r="R39">
+        <v>1.5</v>
+      </c>
+      <c r="S39">
+        <v>2.4</v>
+      </c>
+      <c r="T39">
+        <v>3.2</v>
+      </c>
+      <c r="U39">
+        <v>1.3</v>
+      </c>
+      <c r="V39">
+        <v>8</v>
+      </c>
+      <c r="W39">
+        <v>1.05</v>
+      </c>
+      <c r="X39">
+        <v>1.09</v>
+      </c>
+      <c r="Y39">
+        <v>7</v>
+      </c>
+      <c r="Z39">
+        <v>1.45</v>
+      </c>
+      <c r="AA39">
+        <v>2.7</v>
+      </c>
+      <c r="AB39">
         <v>2.25</v>
       </c>
-      <c r="M39">
-        <v>3.3</v>
-      </c>
-      <c r="N39">
-        <v>2.75</v>
-      </c>
-      <c r="O39">
-        <v>1.73</v>
-      </c>
-      <c r="P39">
-        <v>16.25</v>
-      </c>
-      <c r="Q39">
-        <v>2.1</v>
-      </c>
-      <c r="R39">
-        <v>1.3</v>
-      </c>
-      <c r="S39">
-        <v>3.4</v>
-      </c>
-      <c r="T39">
-        <v>2.25</v>
-      </c>
-      <c r="U39">
-        <v>1.48</v>
-      </c>
-      <c r="V39">
-        <v>5</v>
-      </c>
-      <c r="W39">
-        <v>1.14</v>
-      </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
-      <c r="Y39">
-        <v>0</v>
-      </c>
-      <c r="Z39">
+      <c r="AC39">
+        <v>1.53</v>
+      </c>
+      <c r="AD39">
+        <v>4.5</v>
+      </c>
+      <c r="AE39">
         <v>1.2</v>
       </c>
-      <c r="AA39">
-        <v>4.1</v>
-      </c>
-      <c r="AB39">
-        <v>1.64</v>
-      </c>
-      <c r="AC39">
-        <v>2.05</v>
-      </c>
-      <c r="AD39">
-        <v>2.5</v>
-      </c>
-      <c r="AE39">
-        <v>1.47</v>
-      </c>
       <c r="AF39">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AH39">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="AI39">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ39" t="s">
-        <v>210</v>
+        <v>167</v>
       </c>
       <c r="AK39" t="s">
-        <v>237</v>
-      </c>
-      <c r="AL39">
-        <v>1.25</v>
-      </c>
-      <c r="AM39">
-        <v>1.22</v>
-      </c>
-      <c r="AN39">
-        <v>1.5</v>
-      </c>
-      <c r="AO39">
-        <v>3</v>
-      </c>
-      <c r="AP39">
-        <v>0</v>
-      </c>
-      <c r="AQ39">
-        <v>0</v>
-      </c>
-      <c r="AR39">
-        <v>0</v>
-      </c>
-      <c r="AS39">
-        <v>0</v>
-      </c>
-      <c r="AT39">
-        <v>0</v>
-      </c>
-      <c r="AU39">
-        <v>0</v>
-      </c>
-      <c r="AV39">
-        <v>0</v>
-      </c>
-      <c r="AW39">
-        <v>0</v>
-      </c>
-      <c r="AX39">
-        <v>0</v>
-      </c>
-      <c r="AY39">
-        <v>0</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>1.73</v>
-      </c>
-      <c r="BC39">
-        <v>2.1</v>
-      </c>
-      <c r="BD39" s="3">
+        <v>220</v>
+      </c>
+      <c r="AL39" s="3">
         <v>45757.875</v>
       </c>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:38">
       <c r="A40" s="2">
         <v>45757</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E40" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F40" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -7759,168 +5602,114 @@
         <v>2</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L40">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="M40">
-        <v>2.81</v>
+        <v>4.6</v>
       </c>
       <c r="N40">
-        <v>4.04</v>
+        <v>8.5</v>
       </c>
       <c r="O40">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="P40">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="Q40">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="R40">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="S40">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="T40">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U40">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V40">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="W40">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>6.25</v>
+        <v>9.85</v>
       </c>
       <c r="Z40">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AA40">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="AB40">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AD40">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AE40">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG40">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AH40">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI40">
         <v>1.05</v>
       </c>
       <c r="AJ40" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="AK40" t="s">
-        <v>238</v>
-      </c>
-      <c r="AL40">
-        <v>1.42</v>
-      </c>
-      <c r="AM40">
-        <v>1.33</v>
-      </c>
-      <c r="AN40">
-        <v>1.72</v>
-      </c>
-      <c r="AO40">
-        <v>12</v>
-      </c>
-      <c r="AP40">
-        <v>1.24</v>
-      </c>
-      <c r="AQ40">
-        <v>1.41</v>
-      </c>
-      <c r="AR40">
-        <v>1.73</v>
-      </c>
-      <c r="AS40">
-        <v>2.23</v>
-      </c>
-      <c r="AT40">
-        <v>2.83</v>
-      </c>
-      <c r="AU40">
-        <v>3.52</v>
-      </c>
-      <c r="AV40">
-        <v>2.61</v>
-      </c>
-      <c r="AW40">
-        <v>2</v>
-      </c>
-      <c r="AX40">
-        <v>1.58</v>
-      </c>
-      <c r="AY40">
-        <v>1.38</v>
-      </c>
-      <c r="AZ40">
-        <v>0</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>1.85</v>
-      </c>
-      <c r="BC40">
-        <v>2.4</v>
-      </c>
-      <c r="BD40" s="3">
+        <v>221</v>
+      </c>
+      <c r="AL40" s="3">
         <v>45757.89583333334</v>
       </c>
     </row>
-    <row r="41" spans="1:56">
+    <row r="41" spans="1:38">
       <c r="A41" s="2">
         <v>45757</v>
       </c>
       <c r="B41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
         <v>77</v>
       </c>
-      <c r="C41" t="s">
-        <v>95</v>
-      </c>
       <c r="D41" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E41" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -7929,168 +5718,114 @@
         <v>2</v>
       </c>
       <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>164</v>
+      </c>
+      <c r="L41">
+        <v>2.19</v>
+      </c>
+      <c r="M41">
+        <v>2.81</v>
+      </c>
+      <c r="N41">
+        <v>4.04</v>
+      </c>
+      <c r="O41">
+        <v>1.85</v>
+      </c>
+      <c r="P41">
+        <v>7</v>
+      </c>
+      <c r="Q41">
+        <v>2.4</v>
+      </c>
+      <c r="R41">
+        <v>1.58</v>
+      </c>
+      <c r="S41">
+        <v>2.42</v>
+      </c>
+      <c r="T41">
+        <v>3.34</v>
+      </c>
+      <c r="U41">
+        <v>1.22</v>
+      </c>
+      <c r="V41">
+        <v>10.5</v>
+      </c>
+      <c r="W41">
+        <v>1.01</v>
+      </c>
+      <c r="X41">
+        <v>1.11</v>
+      </c>
+      <c r="Y41">
+        <v>6.25</v>
+      </c>
+      <c r="Z41">
+        <v>1.42</v>
+      </c>
+      <c r="AA41">
+        <v>2.53</v>
+      </c>
+      <c r="AB41">
+        <v>2.4</v>
+      </c>
+      <c r="AC41">
+        <v>1.5</v>
+      </c>
+      <c r="AD41">
+        <v>5</v>
+      </c>
+      <c r="AE41">
+        <v>1.17</v>
+      </c>
+      <c r="AF41">
         <v>2</v>
       </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41" t="s">
-        <v>182</v>
-      </c>
-      <c r="L41">
-        <v>1.36</v>
-      </c>
-      <c r="M41">
-        <v>4.6</v>
-      </c>
-      <c r="N41">
-        <v>8.5</v>
-      </c>
-      <c r="O41">
-        <v>1.29</v>
-      </c>
-      <c r="P41">
-        <v>9.5</v>
-      </c>
-      <c r="Q41">
-        <v>4.5</v>
-      </c>
-      <c r="R41">
-        <v>1.4</v>
-      </c>
-      <c r="S41">
-        <v>2.75</v>
-      </c>
-      <c r="T41">
-        <v>3</v>
-      </c>
-      <c r="U41">
-        <v>1.36</v>
-      </c>
-      <c r="V41">
-        <v>8</v>
-      </c>
-      <c r="W41">
-        <v>1.08</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
-        <v>9.85</v>
-      </c>
-      <c r="Z41">
-        <v>1.28</v>
-      </c>
-      <c r="AA41">
-        <v>3.2</v>
-      </c>
-      <c r="AB41">
-        <v>1.95</v>
-      </c>
-      <c r="AC41">
-        <v>1.79</v>
-      </c>
-      <c r="AD41">
-        <v>3.4</v>
-      </c>
-      <c r="AE41">
-        <v>1.25</v>
-      </c>
-      <c r="AF41">
-        <v>2.38</v>
-      </c>
       <c r="AG41">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AH41">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="AI41">
         <v>1.05</v>
       </c>
       <c r="AJ41" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="AK41" t="s">
-        <v>239</v>
-      </c>
-      <c r="AL41">
-        <v>1.07</v>
-      </c>
-      <c r="AM41">
-        <v>1.15</v>
-      </c>
-      <c r="AN41">
-        <v>2.85</v>
-      </c>
-      <c r="AO41">
-        <v>9</v>
-      </c>
-      <c r="AP41">
-        <v>1.35</v>
-      </c>
-      <c r="AQ41">
-        <v>1.65</v>
-      </c>
-      <c r="AR41">
-        <v>1.93</v>
-      </c>
-      <c r="AS41">
-        <v>2.43</v>
-      </c>
-      <c r="AT41">
-        <v>3.15</v>
-      </c>
-      <c r="AU41">
-        <v>2.9</v>
-      </c>
-      <c r="AV41">
-        <v>2.05</v>
-      </c>
-      <c r="AW41">
-        <v>1.76</v>
-      </c>
-      <c r="AX41">
-        <v>1.47</v>
-      </c>
-      <c r="AY41">
-        <v>1.29</v>
-      </c>
-      <c r="AZ41">
-        <v>0</v>
-      </c>
-      <c r="BA41">
-        <v>0</v>
-      </c>
-      <c r="BB41">
-        <v>1.29</v>
-      </c>
-      <c r="BC41">
-        <v>4.5</v>
-      </c>
-      <c r="BD41" s="3">
+        <v>222</v>
+      </c>
+      <c r="AL41" s="3">
         <v>45757.89583333334</v>
       </c>
     </row>
-    <row r="42" spans="1:56">
+    <row r="42" spans="1:38">
       <c r="A42" s="2">
         <v>45757</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D42" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E42" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F42" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="G42">
         <v>3</v>
@@ -8105,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L42">
         <v>2.18</v>
@@ -8180,66 +5915,12 @@
         <v>1.34</v>
       </c>
       <c r="AJ42" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="AK42" t="s">
-        <v>240</v>
-      </c>
-      <c r="AL42">
-        <v>1.35</v>
-      </c>
-      <c r="AM42">
-        <v>1.18</v>
-      </c>
-      <c r="AN42">
-        <v>1.55</v>
-      </c>
-      <c r="AO42">
-        <v>9</v>
-      </c>
-      <c r="AP42">
-        <v>0</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>1.8</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42">
-        <v>0</v>
-      </c>
-      <c r="AV42">
-        <v>0</v>
-      </c>
-      <c r="AW42">
-        <v>0</v>
-      </c>
-      <c r="AX42">
-        <v>1.91</v>
-      </c>
-      <c r="AY42">
-        <v>0</v>
-      </c>
-      <c r="AZ42">
-        <v>0</v>
-      </c>
-      <c r="BA42">
-        <v>0</v>
-      </c>
-      <c r="BB42">
-        <v>1.75</v>
-      </c>
-      <c r="BC42">
-        <v>1.98</v>
-      </c>
-      <c r="BD42" s="3">
+        <v>223</v>
+      </c>
+      <c r="AL42" s="3">
         <v>45757.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-04-10.xlsx
+++ b/jogos_2025-04-10.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.75</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.11</v>
-      </c>
       <c r="Q8" t="n">
-        <v>4.45</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.88</v>
+        <v>1.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['89', '90+2']</t>
+          <t>['69', '90+2']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.87</v>
+        <v>1.24</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.58</v>
+        <v>2.27</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.52</v>
+        <v>1.97</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45757.45833333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.93</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>2.73</v>
+        <v>3.36</v>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>4.6</v>
+        <v>2.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>4.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.28</v>
+        <v>1.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['69', '90+2']</t>
+          <t>['89', '90+2']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.27</v>
+        <v>1.58</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45757.45833333334</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.03</v>
+        <v>2.34</v>
       </c>
       <c r="M15" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.33</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['16', '53']</t>
         </is>
       </c>
       <c r="AG15" t="n">
         <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45757.54166666666</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="O16" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q16" t="n">
         <v>3.9</v>
@@ -2496,62 +2496,62 @@
         <v>1.35</v>
       </c>
       <c r="S16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.95</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG16" t="n">
         <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45757.54166666666</v>
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA17" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['16', '53']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG17" t="n">
         <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45757.54166666666</v>
@@ -2697,35 +2697,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,19 +2733,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>3.9</v>
@@ -2754,62 +2754,62 @@
         <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="T18" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
         <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG18" t="n">
         <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45757.54166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Adanaspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.96</v>
+        <v>6.01</v>
       </c>
       <c r="M21" t="n">
-        <v>2.6</v>
+        <v>4.06</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>1.51</v>
       </c>
       <c r="O21" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>2.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.96</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>1.85</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>5.2</v>
+        <v>2.72</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>1.79</v>
+        <v>3.48</v>
       </c>
       <c r="Y21" t="n">
-        <v>4</v>
+        <v>1.89</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.300000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '35', '44', '90+2']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.12</v>
+        <v>3.34</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.24</v>
+        <v>1.42</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45757.58333333334</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AA22" t="n">
         <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD22" t="n">
         <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['47', '58', '66']</t>
+          <t>['45+3', '70']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45757.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Adanaspor</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y23" t="n">
         <v>4</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="Z23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.36</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['5', '35', '44', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AI23" t="n">
-        <v>3.34</v>
+        <v>2.12</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.42</v>
+        <v>2.24</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45757.58333333334</v>
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="N25" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AA25" t="n">
         <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD25" t="n">
         <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['45+3', '70']</t>
+          <t>['47', '58', '66']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45757.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.15</v>
+        <v>2.87</v>
       </c>
       <c r="M27" t="n">
-        <v>6.91</v>
+        <v>2.88</v>
       </c>
       <c r="N27" t="n">
-        <v>9.19</v>
+        <v>2.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.18</v>
       </c>
-      <c r="S27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.85</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="X27" t="n">
-        <v>6.65</v>
+        <v>2.2</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['8', '12', '83']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['45+7', '88']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AI27" t="n">
-        <v>1.22</v>
+        <v>2.63</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4.33</v>
+        <v>1.73</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45757.625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P28" t="n">
         <v>3</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>4</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
+        <v>9</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AA28" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['45+7', '88']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['8', '12', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.31</v>
+        <v>4.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.63</v>
+        <v>1.22</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.73</v>
+        <v>4.33</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45757.625</v>
@@ -4761,30 +4761,30 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="n">
-        <v>2</v>
-      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.36</v>
       </c>
-      <c r="M34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>10</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['54', '64']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45757.79166666666</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5044,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="M36" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="O36" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.5</v>
+        <v>4.85</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['22', '84']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45757.79166666666</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>5.15</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>2.51</v>
+        <v>1.91</v>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.85</v>
+        <v>10</v>
       </c>
       <c r="R37" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S37" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="X37" t="n">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AB37" t="n">
         <v>1.17</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['22', '84']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['54', '64']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45757.79166666666</v>
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X38" t="n">
         <v>3.8</v>
       </c>
-      <c r="O38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="Y38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.25</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AH38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['21', '45+2', '71', '75', '76']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45757.83333333334</v>
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P39" t="n">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="R39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1.32</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="AD39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['21', '45+2', '71', '75', '76']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45757.83333333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="M41" t="n">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>3.23</v>
+        <v>2.08</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="R41" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S41" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="T41" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="U41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.3</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.45</v>
-      </c>
       <c r="X41" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '90+3']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45757.875</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>3.23</v>
       </c>
       <c r="O43" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="T43" t="n">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="X43" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['23', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45757.875</v>
